--- a/ModExample/Defs/excel_data/怪物设施配置.xlsx
+++ b/ModExample/Defs/excel_data/怪物设施配置.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58A854A-924A-4C4F-AA6B-58B5A42D50A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D95EE99-EF89-4F02-8C02-D51D5FE01D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2715" yWindow="1335" windowWidth="25020" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monster_facility" sheetId="1" r:id="rId1"/>
@@ -211,10 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>!level#int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>关卡等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -380,6 +376,10 @@
   </si>
   <si>
     <t>成本白银，驭龙之力还需5次维修点满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level#int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -853,7 +853,7 @@
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>41</v>
@@ -948,37 +948,37 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>16</v>
@@ -1035,10 +1035,10 @@
         <v>36</v>
       </c>
       <c r="AF2" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG2" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.15">
@@ -1046,7 +1046,7 @@
         <v>108002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1105,7 +1105,7 @@
         <v>108002</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -1165,7 +1165,7 @@
         <v>108002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -1225,7 +1225,7 @@
         <v>108002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -1288,7 +1288,7 @@
         <v>108002</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
@@ -1351,7 +1351,7 @@
         <v>108002</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="1">
         <v>6</v>
@@ -1414,7 +1414,7 @@
         <v>108002</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1">
         <v>7</v>
@@ -1477,7 +1477,7 @@
         <v>108002</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="1">
         <v>8</v>
@@ -1540,7 +1540,7 @@
         <v>108002</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1">
         <v>9</v>
@@ -1603,7 +1603,7 @@
         <v>108002</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -1666,7 +1666,7 @@
         <v>108002</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1">
         <v>11</v>
@@ -1729,7 +1729,7 @@
         <v>108002</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1">
         <v>12</v>
@@ -1792,7 +1792,7 @@
         <v>108002</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1">
         <v>13</v>
@@ -1855,7 +1855,7 @@
         <v>108002</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1">
         <v>14</v>
@@ -1918,7 +1918,7 @@
         <v>108002</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1">
         <v>15</v>
@@ -1981,7 +1981,7 @@
         <v>108002</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1">
         <v>16</v>
@@ -2044,7 +2044,7 @@
         <v>108002</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1">
         <v>17</v>
@@ -2107,7 +2107,7 @@
         <v>108002</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1">
         <v>18</v>
@@ -2170,7 +2170,7 @@
         <v>108002</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1">
         <v>19</v>
@@ -2233,7 +2233,7 @@
         <v>108002</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1">
         <v>20</v>
@@ -2296,7 +2296,7 @@
         <v>108002</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1">
         <v>21</v>
@@ -2359,7 +2359,7 @@
         <v>108002</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="1">
         <v>22</v>
@@ -2422,7 +2422,7 @@
         <v>108002</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="1">
         <v>23</v>
@@ -2485,7 +2485,7 @@
         <v>108002</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" s="1">
         <v>24</v>
@@ -2548,7 +2548,7 @@
         <v>108002</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" s="1">
         <v>25</v>
@@ -2611,7 +2611,7 @@
         <v>108002</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1">
         <v>26</v>
@@ -2674,7 +2674,7 @@
         <v>108002</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1">
         <v>27</v>
@@ -2737,7 +2737,7 @@
         <v>108002</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -2800,7 +2800,7 @@
         <v>108002</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" s="1">
         <v>29</v>
@@ -2863,7 +2863,7 @@
         <v>108002</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" s="1">
         <v>30</v>
@@ -2947,7 +2947,7 @@
         <v>203020</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J33" s="1">
         <v>10</v>
@@ -2959,7 +2959,7 @@
         <v>607001</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P33" s="1">
         <v>1000</v>
@@ -3024,7 +3024,7 @@
         <v>203028</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J34" s="1">
         <v>2</v>
@@ -3033,7 +3033,7 @@
         <v>608001</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P34" s="1">
         <v>500</v>
@@ -3107,7 +3107,7 @@
         <v>203028</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M35" s="1">
         <v>5</v>
@@ -3193,7 +3193,7 @@
         <v>203022</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J36" s="1">
         <v>50</v>
@@ -3202,7 +3202,7 @@
         <v>203028</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M36" s="1">
         <v>10</v>
@@ -3211,7 +3211,7 @@
         <v>902068</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P36" s="1">
         <v>1</v>
@@ -3220,7 +3220,7 @@
         <v>902070</v>
       </c>
       <c r="R36" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S36" s="1">
         <v>1</v>
@@ -3229,7 +3229,7 @@
         <v>902069</v>
       </c>
       <c r="U36" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V36" s="7">
         <v>1</v>
@@ -3279,7 +3279,7 @@
         <v>203020</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G37" s="1">
         <v>100</v>
@@ -3288,7 +3288,7 @@
         <v>203003</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J37" s="1">
         <v>100</v>
@@ -3300,7 +3300,7 @@
         <v>804001</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P37" s="1">
         <v>1000</v>
@@ -3356,7 +3356,7 @@
         <v>203004</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -3365,7 +3365,7 @@
         <v>203022</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J38" s="1">
         <v>100</v>
@@ -3374,7 +3374,7 @@
         <v>203028</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M38" s="1">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>410003</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P38" s="1">
         <v>1</v>
@@ -3438,7 +3438,7 @@
         <v>203031</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" s="1">
         <v>5</v>
@@ -3456,7 +3456,7 @@
         <v>203034</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M39" s="1">
         <v>50</v>
@@ -3465,7 +3465,7 @@
         <v>413009</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P39" s="1">
         <v>3</v>
@@ -3474,7 +3474,7 @@
         <v>414009</v>
       </c>
       <c r="R39" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S39" s="1">
         <v>3</v>
@@ -3483,7 +3483,7 @@
         <v>415009</v>
       </c>
       <c r="U39" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V39" s="7">
         <v>3</v>
@@ -3533,7 +3533,7 @@
         <v>203031</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G40" s="1">
         <v>10</v>
@@ -3542,7 +3542,7 @@
         <v>203018</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J40" s="1">
         <v>100</v>
@@ -3551,7 +3551,7 @@
         <v>203035</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M40" s="8">
         <v>50</v>
@@ -3560,7 +3560,7 @@
         <v>902071</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P40" s="1">
         <v>1</v>
@@ -3569,7 +3569,7 @@
         <v>902073</v>
       </c>
       <c r="R40" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S40" s="1">
         <v>1</v>
@@ -3578,7 +3578,7 @@
         <v>902072</v>
       </c>
       <c r="U40" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V40" s="7">
         <v>1</v>
@@ -3628,7 +3628,7 @@
         <v>203031</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G41" s="1">
         <v>10</v>
@@ -3637,7 +3637,7 @@
         <v>203001</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J41" s="1">
         <v>50</v>
@@ -3646,7 +3646,7 @@
         <v>203020</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M41" s="1">
         <v>50</v>
@@ -3655,7 +3655,7 @@
         <v>410004</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P41" s="1">
         <v>1</v>
@@ -3705,7 +3705,7 @@
         <v>203031</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G42" s="1">
         <v>5</v>
@@ -3714,7 +3714,7 @@
         <v>203029</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J42" s="1">
         <v>5</v>
@@ -3723,7 +3723,7 @@
         <v>203020</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M42" s="1">
         <v>50</v>
@@ -7469,7 +7469,7 @@
         <v>108008</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C103" s="1">
         <v>1</v>
@@ -7481,7 +7481,7 @@
         <v>203040</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G103" s="1">
         <v>10</v>
@@ -7490,7 +7490,7 @@
         <v>203041</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J103" s="1">
         <v>10</v>
@@ -7528,7 +7528,7 @@
         <v>108008</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C104" s="8">
         <v>2</v>
@@ -7540,7 +7540,7 @@
         <v>203040</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G104" s="1">
         <v>20</v>
@@ -7549,7 +7549,7 @@
         <v>203041</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J104" s="1">
         <v>15</v>
@@ -7587,7 +7587,7 @@
         <v>108008</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C105" s="1">
         <v>3</v>
@@ -7599,7 +7599,7 @@
         <v>203040</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G105" s="1">
         <v>30</v>
@@ -7608,7 +7608,7 @@
         <v>203041</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J105" s="1">
         <v>20</v>
@@ -7646,7 +7646,7 @@
         <v>108008</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C106" s="8">
         <v>4</v>
@@ -7658,7 +7658,7 @@
         <v>203040</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G106" s="1">
         <v>40</v>
@@ -7667,7 +7667,7 @@
         <v>203041</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J106" s="1">
         <v>25</v>
@@ -7705,7 +7705,7 @@
         <v>108008</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C107" s="1">
         <v>5</v>
@@ -7717,7 +7717,7 @@
         <v>203040</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G107" s="1">
         <v>50</v>
@@ -7726,7 +7726,7 @@
         <v>203041</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J107" s="1">
         <v>30</v>
@@ -7764,7 +7764,7 @@
         <v>108008</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C108" s="8">
         <v>6</v>
@@ -7776,7 +7776,7 @@
         <v>203040</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G108" s="1">
         <v>60</v>
@@ -7785,7 +7785,7 @@
         <v>203041</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J108" s="1">
         <v>35</v>
@@ -7823,7 +7823,7 @@
         <v>108008</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C109" s="1">
         <v>7</v>
@@ -7835,7 +7835,7 @@
         <v>203040</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G109" s="1">
         <v>70</v>
@@ -7844,7 +7844,7 @@
         <v>203041</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J109" s="1">
         <v>40</v>
@@ -7882,7 +7882,7 @@
         <v>108008</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C110" s="8">
         <v>8</v>
@@ -7894,7 +7894,7 @@
         <v>203040</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G110" s="1">
         <v>80</v>
@@ -7903,7 +7903,7 @@
         <v>203041</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J110" s="1">
         <v>45</v>
@@ -7941,7 +7941,7 @@
         <v>108008</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C111" s="1">
         <v>9</v>
@@ -7953,7 +7953,7 @@
         <v>203040</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G111" s="1">
         <v>90</v>
@@ -7962,7 +7962,7 @@
         <v>203041</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J111" s="1">
         <v>50</v>
@@ -8000,7 +8000,7 @@
         <v>108008</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C112" s="1">
         <v>10</v>
@@ -8012,7 +8012,7 @@
         <v>203040</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G112" s="1">
         <v>100</v>
@@ -8021,7 +8021,7 @@
         <v>203041</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J112" s="1">
         <v>60</v>
@@ -8059,7 +8059,7 @@
         <v>108011</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
@@ -8071,7 +8071,7 @@
         <v>203058</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G113" s="1">
         <v>10</v>
@@ -8080,7 +8080,7 @@
         <v>203059</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J113" s="1">
         <v>10</v>
@@ -8118,7 +8118,7 @@
         <v>108011</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C114" s="8">
         <v>2</v>
@@ -8130,7 +8130,7 @@
         <v>203058</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G114" s="1">
         <v>20</v>
@@ -8139,7 +8139,7 @@
         <v>203059</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J114" s="1">
         <v>15</v>
@@ -8177,7 +8177,7 @@
         <v>108011</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C115" s="1">
         <v>3</v>
@@ -8189,7 +8189,7 @@
         <v>203058</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G115" s="1">
         <v>30</v>
@@ -8198,7 +8198,7 @@
         <v>203059</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J115" s="1">
         <v>20</v>
@@ -8236,7 +8236,7 @@
         <v>108011</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C116" s="8">
         <v>4</v>
@@ -8248,7 +8248,7 @@
         <v>203058</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G116" s="1">
         <v>40</v>
@@ -8257,7 +8257,7 @@
         <v>203059</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J116" s="1">
         <v>25</v>
@@ -8295,7 +8295,7 @@
         <v>108011</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C117" s="1">
         <v>5</v>
@@ -8307,7 +8307,7 @@
         <v>203058</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G117" s="1">
         <v>50</v>
@@ -8316,7 +8316,7 @@
         <v>203059</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J117" s="1">
         <v>30</v>
@@ -8354,7 +8354,7 @@
         <v>108011</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C118" s="8">
         <v>6</v>
@@ -8366,7 +8366,7 @@
         <v>203058</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G118" s="1">
         <v>60</v>
@@ -8375,7 +8375,7 @@
         <v>203059</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J118" s="1">
         <v>35</v>
@@ -8413,7 +8413,7 @@
         <v>108011</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C119" s="1">
         <v>7</v>
@@ -8425,7 +8425,7 @@
         <v>203058</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G119" s="1">
         <v>70</v>
@@ -8434,7 +8434,7 @@
         <v>203059</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J119" s="1">
         <v>40</v>
@@ -8472,7 +8472,7 @@
         <v>108011</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C120" s="8">
         <v>8</v>
@@ -8484,7 +8484,7 @@
         <v>203058</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G120" s="1">
         <v>80</v>
@@ -8493,7 +8493,7 @@
         <v>203059</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J120" s="1">
         <v>45</v>
@@ -8531,7 +8531,7 @@
         <v>108011</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C121" s="1">
         <v>9</v>
@@ -8543,7 +8543,7 @@
         <v>203058</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G121" s="1">
         <v>90</v>
@@ -8552,7 +8552,7 @@
         <v>203059</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J121" s="1">
         <v>50</v>
@@ -8590,7 +8590,7 @@
         <v>108011</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C122" s="1">
         <v>10</v>
@@ -8602,7 +8602,7 @@
         <v>203058</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G122" s="1">
         <v>100</v>
@@ -8611,7 +8611,7 @@
         <v>203059</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J122" s="1">
         <v>60</v>
@@ -8646,10 +8646,10 @@
     </row>
     <row r="123" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A123" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C123" s="1">
         <v>1</v>
@@ -8668,7 +8668,7 @@
         <v>909005</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P123" s="1">
         <v>2</v>
@@ -8683,7 +8683,7 @@
         <v>608001</v>
       </c>
       <c r="X123" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y123" s="1">
         <v>10</v>
@@ -8701,7 +8701,7 @@
         <v>605001</v>
       </c>
       <c r="AD123" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AE123" s="1">
         <v>200</v>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="124" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A124" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C124" s="1">
         <v>2</v>
@@ -8731,7 +8731,7 @@
         <v>909005</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P124" s="1">
         <v>2</v>
@@ -8746,7 +8746,7 @@
         <v>608001</v>
       </c>
       <c r="X124" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y124" s="1">
         <v>20</v>
@@ -8764,7 +8764,7 @@
         <v>605001</v>
       </c>
       <c r="AD124" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AE124" s="1">
         <v>200</v>
@@ -8772,10 +8772,10 @@
     </row>
     <row r="125" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A125" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C125" s="1">
         <v>3</v>
@@ -8794,7 +8794,7 @@
         <v>909005</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P125" s="1">
         <v>2</v>
@@ -8809,7 +8809,7 @@
         <v>608001</v>
       </c>
       <c r="X125" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y125" s="1">
         <v>30</v>
@@ -8827,7 +8827,7 @@
         <v>605001</v>
       </c>
       <c r="AD125" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AE125" s="10">
         <v>200</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="126" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A126" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C126" s="1">
         <v>4</v>
@@ -8857,7 +8857,7 @@
         <v>909005</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P126" s="1">
         <f>P123+1</f>
@@ -8873,7 +8873,7 @@
         <v>608001</v>
       </c>
       <c r="X126" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y126" s="1">
         <v>40</v>
@@ -8882,7 +8882,7 @@
         <v>612001</v>
       </c>
       <c r="AA126" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB126" s="1">
         <v>100</v>
@@ -8895,15 +8895,15 @@
         <v>900</v>
       </c>
       <c r="AG126" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A127" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C127" s="1">
         <v>5</v>
@@ -8922,7 +8922,7 @@
         <v>909005</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P127" s="1">
         <f t="shared" ref="P127:P190" si="10">P124+1</f>
@@ -8938,7 +8938,7 @@
         <v>608001</v>
       </c>
       <c r="X127" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y127" s="1">
         <v>50</v>
@@ -8947,7 +8947,7 @@
         <v>612002</v>
       </c>
       <c r="AA127" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB127" s="1">
         <v>150</v>
@@ -8960,15 +8960,15 @@
         <v>1250</v>
       </c>
       <c r="AG127" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="128" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A128" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C128" s="1">
         <v>6</v>
@@ -8987,7 +8987,7 @@
         <v>909005</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P128" s="1">
         <f t="shared" si="10"/>
@@ -9003,7 +9003,7 @@
         <v>608001</v>
       </c>
       <c r="X128" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y128" s="1">
         <v>60</v>
@@ -9012,7 +9012,7 @@
         <v>612003</v>
       </c>
       <c r="AA128" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB128" s="1">
         <v>200</v>
@@ -9025,15 +9025,15 @@
         <v>1600</v>
       </c>
       <c r="AG128" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A129" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C129" s="1">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>909005</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P129" s="1">
         <f t="shared" si="10"/>
@@ -9068,7 +9068,7 @@
         <v>608001</v>
       </c>
       <c r="X129" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y129" s="1">
         <v>70</v>
@@ -9077,7 +9077,7 @@
         <v>612001</v>
       </c>
       <c r="AA129" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB129" s="1">
         <v>250</v>
@@ -9090,15 +9090,15 @@
         <v>1950</v>
       </c>
       <c r="AG129" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A130" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C130" s="1">
         <v>8</v>
@@ -9117,7 +9117,7 @@
         <v>909005</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P130" s="1">
         <f t="shared" si="10"/>
@@ -9133,7 +9133,7 @@
         <v>608001</v>
       </c>
       <c r="X130" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y130" s="1">
         <v>80</v>
@@ -9142,7 +9142,7 @@
         <v>612002</v>
       </c>
       <c r="AA130" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB130" s="1">
         <v>300</v>
@@ -9155,15 +9155,15 @@
         <v>2300</v>
       </c>
       <c r="AG130" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A131" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C131" s="1">
         <v>9</v>
@@ -9182,7 +9182,7 @@
         <v>909005</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P131" s="1">
         <f t="shared" si="10"/>
@@ -9198,7 +9198,7 @@
         <v>608001</v>
       </c>
       <c r="X131" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y131" s="1">
         <v>90</v>
@@ -9207,7 +9207,7 @@
         <v>612003</v>
       </c>
       <c r="AA131" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB131" s="1">
         <v>350</v>
@@ -9220,15 +9220,15 @@
         <v>2650</v>
       </c>
       <c r="AG131" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="132" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A132" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C132" s="1">
         <v>10</v>
@@ -9247,7 +9247,7 @@
         <v>909005</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P132" s="1">
         <f t="shared" si="10"/>
@@ -9263,7 +9263,7 @@
         <v>608001</v>
       </c>
       <c r="X132" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y132" s="1">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>612001</v>
       </c>
       <c r="AA132" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB132" s="1">
         <v>400</v>
@@ -9285,15 +9285,15 @@
         <v>3000</v>
       </c>
       <c r="AG132" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A133" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C133" s="1">
         <v>11</v>
@@ -9312,7 +9312,7 @@
         <v>909005</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P133" s="1">
         <f t="shared" si="10"/>
@@ -9328,7 +9328,7 @@
         <v>608001</v>
       </c>
       <c r="X133" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y133" s="1">
         <v>110</v>
@@ -9337,7 +9337,7 @@
         <v>612002</v>
       </c>
       <c r="AA133" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB133" s="1">
         <v>450</v>
@@ -9350,15 +9350,15 @@
         <v>3350</v>
       </c>
       <c r="AG133" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A134" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B134" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C134" s="1">
         <v>12</v>
@@ -9377,7 +9377,7 @@
         <v>909005</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P134" s="1">
         <f t="shared" si="10"/>
@@ -9393,7 +9393,7 @@
         <v>608001</v>
       </c>
       <c r="X134" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y134" s="1">
         <v>120</v>
@@ -9402,7 +9402,7 @@
         <v>612003</v>
       </c>
       <c r="AA134" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB134" s="1">
         <v>500</v>
@@ -9415,15 +9415,15 @@
         <v>3700</v>
       </c>
       <c r="AG134" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="135" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A135" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C135" s="1">
         <v>13</v>
@@ -9442,7 +9442,7 @@
         <v>909005</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P135" s="1">
         <f t="shared" si="10"/>
@@ -9458,7 +9458,7 @@
         <v>608001</v>
       </c>
       <c r="X135" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y135" s="1">
         <v>130</v>
@@ -9467,7 +9467,7 @@
         <v>612001</v>
       </c>
       <c r="AA135" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB135" s="1">
         <v>550</v>
@@ -9480,15 +9480,15 @@
         <v>4050</v>
       </c>
       <c r="AG135" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="136" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A136" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B136" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C136" s="1">
         <v>14</v>
@@ -9507,7 +9507,7 @@
         <v>909005</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P136" s="1">
         <f t="shared" si="10"/>
@@ -9523,7 +9523,7 @@
         <v>608001</v>
       </c>
       <c r="X136" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y136" s="1">
         <v>140</v>
@@ -9532,7 +9532,7 @@
         <v>612002</v>
       </c>
       <c r="AA136" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB136" s="1">
         <v>600</v>
@@ -9545,15 +9545,15 @@
         <v>4400</v>
       </c>
       <c r="AG136" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A137" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B137" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C137" s="1">
         <v>15</v>
@@ -9572,7 +9572,7 @@
         <v>909005</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P137" s="1">
         <f t="shared" si="10"/>
@@ -9588,7 +9588,7 @@
         <v>608001</v>
       </c>
       <c r="X137" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y137" s="1">
         <v>150</v>
@@ -9597,7 +9597,7 @@
         <v>612003</v>
       </c>
       <c r="AA137" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB137" s="1">
         <v>650</v>
@@ -9610,15 +9610,15 @@
         <v>4750</v>
       </c>
       <c r="AG137" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A138" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B138" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C138" s="1">
         <v>16</v>
@@ -9637,7 +9637,7 @@
         <v>909005</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P138" s="1">
         <f t="shared" si="10"/>
@@ -9653,7 +9653,7 @@
         <v>608001</v>
       </c>
       <c r="X138" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y138" s="1">
         <v>160</v>
@@ -9662,7 +9662,7 @@
         <v>612001</v>
       </c>
       <c r="AA138" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB138" s="1">
         <v>700</v>
@@ -9675,15 +9675,15 @@
         <v>5100</v>
       </c>
       <c r="AG138" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="139" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A139" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B139" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C139" s="1">
         <v>17</v>
@@ -9702,7 +9702,7 @@
         <v>909005</v>
       </c>
       <c r="O139" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P139" s="1">
         <f t="shared" si="10"/>
@@ -9718,7 +9718,7 @@
         <v>608001</v>
       </c>
       <c r="X139" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y139" s="1">
         <v>170</v>
@@ -9727,7 +9727,7 @@
         <v>612002</v>
       </c>
       <c r="AA139" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB139" s="1">
         <v>750</v>
@@ -9740,15 +9740,15 @@
         <v>5450</v>
       </c>
       <c r="AG139" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="140" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A140" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B140" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C140" s="1">
         <v>18</v>
@@ -9767,7 +9767,7 @@
         <v>909005</v>
       </c>
       <c r="O140" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P140" s="1">
         <f t="shared" si="10"/>
@@ -9783,7 +9783,7 @@
         <v>608001</v>
       </c>
       <c r="X140" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y140" s="1">
         <v>180</v>
@@ -9792,7 +9792,7 @@
         <v>612003</v>
       </c>
       <c r="AA140" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB140" s="1">
         <v>800</v>
@@ -9805,15 +9805,15 @@
         <v>5800</v>
       </c>
       <c r="AG140" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A141" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B141" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C141" s="1">
         <v>19</v>
@@ -9832,7 +9832,7 @@
         <v>909005</v>
       </c>
       <c r="O141" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P141" s="1">
         <f t="shared" si="10"/>
@@ -9848,7 +9848,7 @@
         <v>608001</v>
       </c>
       <c r="X141" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y141" s="1">
         <v>190</v>
@@ -9857,7 +9857,7 @@
         <v>612001</v>
       </c>
       <c r="AA141" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB141" s="1">
         <v>850</v>
@@ -9870,15 +9870,15 @@
         <v>6150</v>
       </c>
       <c r="AG141" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A142" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B142" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C142" s="1">
         <v>20</v>
@@ -9897,7 +9897,7 @@
         <v>909005</v>
       </c>
       <c r="O142" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P142" s="1">
         <f t="shared" si="10"/>
@@ -9913,7 +9913,7 @@
         <v>608001</v>
       </c>
       <c r="X142" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y142" s="1">
         <v>200</v>
@@ -9922,7 +9922,7 @@
         <v>612002</v>
       </c>
       <c r="AA142" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB142" s="1">
         <v>900</v>
@@ -9935,15 +9935,15 @@
         <v>6500</v>
       </c>
       <c r="AG142" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A143" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C143" s="1">
         <v>21</v>
@@ -9962,7 +9962,7 @@
         <v>909005</v>
       </c>
       <c r="O143" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P143" s="1">
         <f t="shared" si="10"/>
@@ -9978,7 +9978,7 @@
         <v>608001</v>
       </c>
       <c r="X143" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y143" s="1">
         <v>210</v>
@@ -9987,7 +9987,7 @@
         <v>612003</v>
       </c>
       <c r="AA143" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB143" s="1">
         <v>950</v>
@@ -10000,15 +10000,15 @@
         <v>6850</v>
       </c>
       <c r="AG143" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="144" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A144" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B144" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C144" s="1">
         <v>22</v>
@@ -10027,7 +10027,7 @@
         <v>909005</v>
       </c>
       <c r="O144" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P144" s="1">
         <f t="shared" si="10"/>
@@ -10043,7 +10043,7 @@
         <v>608001</v>
       </c>
       <c r="X144" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y144" s="1">
         <v>220</v>
@@ -10052,7 +10052,7 @@
         <v>612001</v>
       </c>
       <c r="AA144" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB144" s="1">
         <v>1000</v>
@@ -10065,15 +10065,15 @@
         <v>7200</v>
       </c>
       <c r="AG144" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="145" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A145" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B145" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C145" s="1">
         <v>23</v>
@@ -10092,7 +10092,7 @@
         <v>909005</v>
       </c>
       <c r="O145" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P145" s="1">
         <f t="shared" si="10"/>
@@ -10108,7 +10108,7 @@
         <v>608001</v>
       </c>
       <c r="X145" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y145" s="1">
         <v>230</v>
@@ -10117,7 +10117,7 @@
         <v>612002</v>
       </c>
       <c r="AA145" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB145" s="1">
         <v>1100</v>
@@ -10130,15 +10130,15 @@
         <v>7800</v>
       </c>
       <c r="AG145" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="146" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A146" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C146" s="1">
         <v>24</v>
@@ -10157,7 +10157,7 @@
         <v>909005</v>
       </c>
       <c r="O146" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P146" s="1">
         <f t="shared" si="10"/>
@@ -10173,7 +10173,7 @@
         <v>608001</v>
       </c>
       <c r="X146" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y146" s="1">
         <v>240</v>
@@ -10182,7 +10182,7 @@
         <v>612003</v>
       </c>
       <c r="AA146" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB146" s="1">
         <v>1200</v>
@@ -10195,15 +10195,15 @@
         <v>8400</v>
       </c>
       <c r="AG146" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="147" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A147" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B147" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C147" s="1">
         <v>25</v>
@@ -10222,7 +10222,7 @@
         <v>909005</v>
       </c>
       <c r="O147" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P147" s="1">
         <f t="shared" si="10"/>
@@ -10238,7 +10238,7 @@
         <v>608001</v>
       </c>
       <c r="X147" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y147" s="1">
         <v>250</v>
@@ -10247,7 +10247,7 @@
         <v>612001</v>
       </c>
       <c r="AA147" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB147" s="1">
         <v>1300</v>
@@ -10260,15 +10260,15 @@
         <v>9000</v>
       </c>
       <c r="AG147" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A148" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C148" s="1">
         <v>26</v>
@@ -10287,7 +10287,7 @@
         <v>909005</v>
       </c>
       <c r="O148" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P148" s="1">
         <f t="shared" si="10"/>
@@ -10303,7 +10303,7 @@
         <v>608001</v>
       </c>
       <c r="X148" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y148" s="1">
         <v>260</v>
@@ -10312,7 +10312,7 @@
         <v>612002</v>
       </c>
       <c r="AA148" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB148" s="1">
         <v>1400</v>
@@ -10325,15 +10325,15 @@
         <v>9600</v>
       </c>
       <c r="AG148" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="149" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A149" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C149" s="1">
         <v>27</v>
@@ -10352,7 +10352,7 @@
         <v>909005</v>
       </c>
       <c r="O149" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P149" s="1">
         <f t="shared" si="10"/>
@@ -10368,7 +10368,7 @@
         <v>608001</v>
       </c>
       <c r="X149" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y149" s="1">
         <v>270</v>
@@ -10377,7 +10377,7 @@
         <v>612003</v>
       </c>
       <c r="AA149" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB149" s="1">
         <v>1500</v>
@@ -10390,15 +10390,15 @@
         <v>10200</v>
       </c>
       <c r="AG149" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="150" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A150" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C150" s="1">
         <v>28</v>
@@ -10417,7 +10417,7 @@
         <v>909005</v>
       </c>
       <c r="O150" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P150" s="1">
         <f t="shared" si="10"/>
@@ -10433,7 +10433,7 @@
         <v>608001</v>
       </c>
       <c r="X150" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y150" s="1">
         <v>280</v>
@@ -10442,7 +10442,7 @@
         <v>612001</v>
       </c>
       <c r="AA150" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB150" s="1">
         <v>1600</v>
@@ -10455,15 +10455,15 @@
         <v>10800</v>
       </c>
       <c r="AG150" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="151" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A151" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C151" s="1">
         <v>29</v>
@@ -10482,7 +10482,7 @@
         <v>909005</v>
       </c>
       <c r="O151" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P151" s="1">
         <f t="shared" si="10"/>
@@ -10498,7 +10498,7 @@
         <v>608001</v>
       </c>
       <c r="X151" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y151" s="1">
         <v>290</v>
@@ -10507,7 +10507,7 @@
         <v>612002</v>
       </c>
       <c r="AA151" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB151" s="1">
         <v>1700</v>
@@ -10520,15 +10520,15 @@
         <v>11400</v>
       </c>
       <c r="AG151" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="152" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A152" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C152" s="1">
         <v>30</v>
@@ -10547,7 +10547,7 @@
         <v>909005</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P152" s="1">
         <f t="shared" si="10"/>
@@ -10563,7 +10563,7 @@
         <v>608001</v>
       </c>
       <c r="X152" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y152" s="1">
         <v>300</v>
@@ -10572,7 +10572,7 @@
         <v>612003</v>
       </c>
       <c r="AA152" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB152" s="1">
         <v>1800</v>
@@ -10585,15 +10585,15 @@
         <v>12000</v>
       </c>
       <c r="AG152" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A153" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B153" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C153" s="1">
         <v>31</v>
@@ -10612,7 +10612,7 @@
         <v>909005</v>
       </c>
       <c r="O153" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P153" s="1">
         <f t="shared" si="10"/>
@@ -10628,7 +10628,7 @@
         <v>608001</v>
       </c>
       <c r="X153" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y153" s="1">
         <v>310</v>
@@ -10637,7 +10637,7 @@
         <v>612001</v>
       </c>
       <c r="AA153" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB153" s="1">
         <v>1900</v>
@@ -10650,15 +10650,15 @@
         <v>12600</v>
       </c>
       <c r="AG153" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A154" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B154" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C154" s="1">
         <v>32</v>
@@ -10677,7 +10677,7 @@
         <v>909005</v>
       </c>
       <c r="O154" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P154" s="1">
         <f t="shared" si="10"/>
@@ -10693,7 +10693,7 @@
         <v>608001</v>
       </c>
       <c r="X154" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y154" s="1">
         <v>320</v>
@@ -10702,7 +10702,7 @@
         <v>612002</v>
       </c>
       <c r="AA154" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB154" s="1">
         <v>2000</v>
@@ -10715,15 +10715,15 @@
         <v>13200</v>
       </c>
       <c r="AG154" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="155" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A155" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C155" s="1">
         <v>33</v>
@@ -10742,7 +10742,7 @@
         <v>909005</v>
       </c>
       <c r="O155" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P155" s="1">
         <f t="shared" si="10"/>
@@ -10758,7 +10758,7 @@
         <v>608001</v>
       </c>
       <c r="X155" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y155" s="1">
         <v>330</v>
@@ -10767,7 +10767,7 @@
         <v>612003</v>
       </c>
       <c r="AA155" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB155" s="1">
         <v>2100</v>
@@ -10780,15 +10780,15 @@
         <v>13800</v>
       </c>
       <c r="AG155" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="156" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A156" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B156" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C156" s="1">
         <v>34</v>
@@ -10807,7 +10807,7 @@
         <v>909005</v>
       </c>
       <c r="O156" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P156" s="1">
         <f t="shared" si="10"/>
@@ -10823,7 +10823,7 @@
         <v>608001</v>
       </c>
       <c r="X156" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y156" s="1">
         <v>340</v>
@@ -10832,7 +10832,7 @@
         <v>612001</v>
       </c>
       <c r="AA156" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB156" s="1">
         <v>2200</v>
@@ -10845,15 +10845,15 @@
         <v>14400</v>
       </c>
       <c r="AG156" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A157" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C157" s="1">
         <v>35</v>
@@ -10872,7 +10872,7 @@
         <v>909005</v>
       </c>
       <c r="O157" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P157" s="1">
         <f t="shared" si="10"/>
@@ -10888,7 +10888,7 @@
         <v>608001</v>
       </c>
       <c r="X157" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y157" s="1">
         <v>350</v>
@@ -10897,7 +10897,7 @@
         <v>612002</v>
       </c>
       <c r="AA157" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB157" s="1">
         <v>2300</v>
@@ -10910,15 +10910,15 @@
         <v>15000</v>
       </c>
       <c r="AG157" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="158" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A158" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B158" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C158" s="1">
         <v>36</v>
@@ -10937,7 +10937,7 @@
         <v>909005</v>
       </c>
       <c r="O158" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P158" s="1">
         <f t="shared" si="10"/>
@@ -10953,7 +10953,7 @@
         <v>608001</v>
       </c>
       <c r="X158" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y158" s="1">
         <v>360</v>
@@ -10962,7 +10962,7 @@
         <v>612003</v>
       </c>
       <c r="AA158" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB158" s="1">
         <v>2400</v>
@@ -10975,15 +10975,15 @@
         <v>15600</v>
       </c>
       <c r="AG158" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A159" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B159" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C159" s="1">
         <v>37</v>
@@ -11002,7 +11002,7 @@
         <v>909005</v>
       </c>
       <c r="O159" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P159" s="1">
         <f t="shared" si="10"/>
@@ -11018,7 +11018,7 @@
         <v>608001</v>
       </c>
       <c r="X159" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y159" s="1">
         <v>370</v>
@@ -11027,7 +11027,7 @@
         <v>612001</v>
       </c>
       <c r="AA159" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB159" s="1">
         <v>2500</v>
@@ -11040,15 +11040,15 @@
         <v>16200</v>
       </c>
       <c r="AG159" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="160" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A160" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B160" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C160" s="1">
         <v>38</v>
@@ -11067,7 +11067,7 @@
         <v>909005</v>
       </c>
       <c r="O160" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P160" s="1">
         <f t="shared" si="10"/>
@@ -11083,7 +11083,7 @@
         <v>608001</v>
       </c>
       <c r="X160" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y160" s="1">
         <v>380</v>
@@ -11092,7 +11092,7 @@
         <v>612002</v>
       </c>
       <c r="AA160" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB160" s="1">
         <v>2600</v>
@@ -11105,15 +11105,15 @@
         <v>16800</v>
       </c>
       <c r="AG160" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="161" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A161" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B161" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C161" s="1">
         <v>39</v>
@@ -11132,7 +11132,7 @@
         <v>909005</v>
       </c>
       <c r="O161" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P161" s="1">
         <f t="shared" si="10"/>
@@ -11148,7 +11148,7 @@
         <v>608001</v>
       </c>
       <c r="X161" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y161" s="1">
         <v>390</v>
@@ -11157,7 +11157,7 @@
         <v>612003</v>
       </c>
       <c r="AA161" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB161" s="1">
         <v>2700</v>
@@ -11170,15 +11170,15 @@
         <v>17400</v>
       </c>
       <c r="AG161" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="162" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A162" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B162" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C162" s="1">
         <v>40</v>
@@ -11197,7 +11197,7 @@
         <v>909005</v>
       </c>
       <c r="O162" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P162" s="1">
         <f t="shared" si="10"/>
@@ -11213,7 +11213,7 @@
         <v>608001</v>
       </c>
       <c r="X162" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y162" s="1">
         <v>400</v>
@@ -11222,7 +11222,7 @@
         <v>612001</v>
       </c>
       <c r="AA162" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB162" s="1">
         <v>2800</v>
@@ -11235,15 +11235,15 @@
         <v>18000</v>
       </c>
       <c r="AG162" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A163" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B163" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C163" s="1">
         <v>41</v>
@@ -11262,7 +11262,7 @@
         <v>909005</v>
       </c>
       <c r="O163" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P163" s="1">
         <f t="shared" si="10"/>
@@ -11278,7 +11278,7 @@
         <v>608001</v>
       </c>
       <c r="X163" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y163" s="1">
         <v>410</v>
@@ -11287,7 +11287,7 @@
         <v>612002</v>
       </c>
       <c r="AA163" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB163" s="1">
         <v>2900</v>
@@ -11300,15 +11300,15 @@
         <v>18600</v>
       </c>
       <c r="AG163" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="164" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A164" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B164" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C164" s="1">
         <v>42</v>
@@ -11327,7 +11327,7 @@
         <v>909005</v>
       </c>
       <c r="O164" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P164" s="1">
         <f t="shared" si="10"/>
@@ -11343,7 +11343,7 @@
         <v>608001</v>
       </c>
       <c r="X164" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y164" s="1">
         <v>420</v>
@@ -11352,7 +11352,7 @@
         <v>612003</v>
       </c>
       <c r="AA164" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB164" s="1">
         <v>3000</v>
@@ -11365,15 +11365,15 @@
         <v>19200</v>
       </c>
       <c r="AG164" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="165" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A165" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B165" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C165" s="1">
         <v>43</v>
@@ -11392,7 +11392,7 @@
         <v>909005</v>
       </c>
       <c r="O165" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P165" s="1">
         <f t="shared" si="10"/>
@@ -11408,7 +11408,7 @@
         <v>608001</v>
       </c>
       <c r="X165" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y165" s="1">
         <v>430</v>
@@ -11417,7 +11417,7 @@
         <v>612001</v>
       </c>
       <c r="AA165" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB165" s="1">
         <v>3100</v>
@@ -11430,15 +11430,15 @@
         <v>19800</v>
       </c>
       <c r="AG165" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="166" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A166" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B166" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C166" s="1">
         <v>44</v>
@@ -11457,7 +11457,7 @@
         <v>909005</v>
       </c>
       <c r="O166" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P166" s="1">
         <f t="shared" si="10"/>
@@ -11473,7 +11473,7 @@
         <v>608001</v>
       </c>
       <c r="X166" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y166" s="1">
         <v>440</v>
@@ -11482,7 +11482,7 @@
         <v>612002</v>
       </c>
       <c r="AA166" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB166" s="1">
         <v>3200</v>
@@ -11495,15 +11495,15 @@
         <v>20400</v>
       </c>
       <c r="AG166" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="167" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A167" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B167" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C167" s="1">
         <v>45</v>
@@ -11522,7 +11522,7 @@
         <v>909005</v>
       </c>
       <c r="O167" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P167" s="1">
         <f t="shared" si="10"/>
@@ -11538,7 +11538,7 @@
         <v>608001</v>
       </c>
       <c r="X167" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y167" s="1">
         <v>450</v>
@@ -11547,7 +11547,7 @@
         <v>612003</v>
       </c>
       <c r="AA167" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB167" s="1">
         <v>3300</v>
@@ -11560,15 +11560,15 @@
         <v>21000</v>
       </c>
       <c r="AG167" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="168" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A168" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B168" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C168" s="1">
         <v>46</v>
@@ -11587,7 +11587,7 @@
         <v>909005</v>
       </c>
       <c r="O168" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P168" s="1">
         <f t="shared" si="10"/>
@@ -11603,7 +11603,7 @@
         <v>608001</v>
       </c>
       <c r="X168" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="1">
         <v>460</v>
@@ -11612,7 +11612,7 @@
         <v>612001</v>
       </c>
       <c r="AA168" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB168" s="1">
         <v>3400</v>
@@ -11625,15 +11625,15 @@
         <v>21600</v>
       </c>
       <c r="AG168" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="169" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A169" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B169" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C169" s="1">
         <v>47</v>
@@ -11652,7 +11652,7 @@
         <v>909005</v>
       </c>
       <c r="O169" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P169" s="1">
         <f t="shared" si="10"/>
@@ -11668,7 +11668,7 @@
         <v>608001</v>
       </c>
       <c r="X169" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y169" s="1">
         <v>470</v>
@@ -11677,7 +11677,7 @@
         <v>612002</v>
       </c>
       <c r="AA169" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB169" s="1">
         <v>3500</v>
@@ -11690,15 +11690,15 @@
         <v>22200</v>
       </c>
       <c r="AG169" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="170" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A170" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B170" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C170" s="1">
         <v>48</v>
@@ -11717,7 +11717,7 @@
         <v>909005</v>
       </c>
       <c r="O170" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P170" s="1">
         <f t="shared" si="10"/>
@@ -11733,7 +11733,7 @@
         <v>608001</v>
       </c>
       <c r="X170" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y170" s="1">
         <v>480</v>
@@ -11742,7 +11742,7 @@
         <v>612003</v>
       </c>
       <c r="AA170" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB170" s="1">
         <v>3600</v>
@@ -11755,15 +11755,15 @@
         <v>22800</v>
       </c>
       <c r="AG170" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="171" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A171" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B171" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C171" s="1">
         <v>49</v>
@@ -11782,7 +11782,7 @@
         <v>909005</v>
       </c>
       <c r="O171" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P171" s="1">
         <f t="shared" si="10"/>
@@ -11798,7 +11798,7 @@
         <v>608001</v>
       </c>
       <c r="X171" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y171" s="1">
         <v>490</v>
@@ -11807,7 +11807,7 @@
         <v>612001</v>
       </c>
       <c r="AA171" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB171" s="1">
         <v>3700</v>
@@ -11820,15 +11820,15 @@
         <v>23400</v>
       </c>
       <c r="AG171" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="172" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A172" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B172" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C172" s="1">
         <v>50</v>
@@ -11847,7 +11847,7 @@
         <v>909005</v>
       </c>
       <c r="O172" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P172" s="1">
         <f t="shared" si="10"/>
@@ -11863,7 +11863,7 @@
         <v>608001</v>
       </c>
       <c r="X172" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y172" s="1">
         <v>500</v>
@@ -11872,7 +11872,7 @@
         <v>612002</v>
       </c>
       <c r="AA172" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB172" s="1">
         <v>3800</v>
@@ -11885,15 +11885,15 @@
         <v>24000</v>
       </c>
       <c r="AG172" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="173" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A173" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B173" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C173" s="1">
         <v>51</v>
@@ -11912,7 +11912,7 @@
         <v>909005</v>
       </c>
       <c r="O173" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P173" s="1">
         <f t="shared" si="10"/>
@@ -11928,7 +11928,7 @@
         <v>608001</v>
       </c>
       <c r="X173" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y173" s="1">
         <v>510</v>
@@ -11937,7 +11937,7 @@
         <v>612003</v>
       </c>
       <c r="AA173" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB173" s="1">
         <v>3900</v>
@@ -11950,15 +11950,15 @@
         <v>24600</v>
       </c>
       <c r="AG173" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="174" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A174" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B174" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C174" s="1">
         <v>52</v>
@@ -11977,7 +11977,7 @@
         <v>909005</v>
       </c>
       <c r="O174" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P174" s="1">
         <f t="shared" si="10"/>
@@ -11993,7 +11993,7 @@
         <v>608001</v>
       </c>
       <c r="X174" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y174" s="1">
         <v>520</v>
@@ -12002,7 +12002,7 @@
         <v>612001</v>
       </c>
       <c r="AA174" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB174" s="1">
         <v>4000</v>
@@ -12015,15 +12015,15 @@
         <v>25200</v>
       </c>
       <c r="AG174" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="175" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A175" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B175" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C175" s="1">
         <v>53</v>
@@ -12042,7 +12042,7 @@
         <v>909005</v>
       </c>
       <c r="O175" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P175" s="1">
         <f t="shared" si="10"/>
@@ -12058,7 +12058,7 @@
         <v>608001</v>
       </c>
       <c r="X175" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y175" s="1">
         <v>530</v>
@@ -12067,7 +12067,7 @@
         <v>612002</v>
       </c>
       <c r="AA175" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB175" s="1">
         <v>4100</v>
@@ -12080,15 +12080,15 @@
         <v>25800</v>
       </c>
       <c r="AG175" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="176" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A176" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B176" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C176" s="1">
         <v>54</v>
@@ -12107,7 +12107,7 @@
         <v>909005</v>
       </c>
       <c r="O176" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P176" s="1">
         <f t="shared" si="10"/>
@@ -12123,7 +12123,7 @@
         <v>608001</v>
       </c>
       <c r="X176" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y176" s="1">
         <v>540</v>
@@ -12132,7 +12132,7 @@
         <v>612003</v>
       </c>
       <c r="AA176" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB176" s="1">
         <v>4200</v>
@@ -12145,15 +12145,15 @@
         <v>26400</v>
       </c>
       <c r="AG176" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="177" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A177" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B177" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C177" s="1">
         <v>55</v>
@@ -12172,7 +12172,7 @@
         <v>909005</v>
       </c>
       <c r="O177" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P177" s="1">
         <f t="shared" si="10"/>
@@ -12188,7 +12188,7 @@
         <v>608001</v>
       </c>
       <c r="X177" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y177" s="1">
         <v>550</v>
@@ -12197,7 +12197,7 @@
         <v>612001</v>
       </c>
       <c r="AA177" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB177" s="1">
         <v>4300</v>
@@ -12210,15 +12210,15 @@
         <v>27000</v>
       </c>
       <c r="AG177" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="178" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A178" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B178" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C178" s="1">
         <v>56</v>
@@ -12237,7 +12237,7 @@
         <v>909005</v>
       </c>
       <c r="O178" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P178" s="1">
         <f t="shared" si="10"/>
@@ -12253,7 +12253,7 @@
         <v>608001</v>
       </c>
       <c r="X178" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y178" s="1">
         <v>560</v>
@@ -12262,7 +12262,7 @@
         <v>612002</v>
       </c>
       <c r="AA178" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB178" s="1">
         <v>4400</v>
@@ -12275,15 +12275,15 @@
         <v>27600</v>
       </c>
       <c r="AG178" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="179" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A179" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B179" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C179" s="1">
         <v>57</v>
@@ -12302,7 +12302,7 @@
         <v>909005</v>
       </c>
       <c r="O179" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P179" s="1">
         <f t="shared" si="10"/>
@@ -12318,7 +12318,7 @@
         <v>608001</v>
       </c>
       <c r="X179" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y179" s="1">
         <v>570</v>
@@ -12327,7 +12327,7 @@
         <v>612003</v>
       </c>
       <c r="AA179" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB179" s="1">
         <v>4500</v>
@@ -12340,15 +12340,15 @@
         <v>28200</v>
       </c>
       <c r="AG179" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="180" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A180" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B180" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C180" s="1">
         <v>58</v>
@@ -12367,7 +12367,7 @@
         <v>909005</v>
       </c>
       <c r="O180" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P180" s="1">
         <f t="shared" si="10"/>
@@ -12383,7 +12383,7 @@
         <v>608001</v>
       </c>
       <c r="X180" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y180" s="1">
         <v>580</v>
@@ -12392,7 +12392,7 @@
         <v>612001</v>
       </c>
       <c r="AA180" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB180" s="1">
         <v>4600</v>
@@ -12405,15 +12405,15 @@
         <v>28800</v>
       </c>
       <c r="AG180" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="181" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A181" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B181" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C181" s="1">
         <v>59</v>
@@ -12432,7 +12432,7 @@
         <v>909005</v>
       </c>
       <c r="O181" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P181" s="1">
         <f t="shared" si="10"/>
@@ -12448,7 +12448,7 @@
         <v>608001</v>
       </c>
       <c r="X181" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y181" s="1">
         <v>590</v>
@@ -12457,7 +12457,7 @@
         <v>612002</v>
       </c>
       <c r="AA181" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB181" s="1">
         <v>4700</v>
@@ -12470,15 +12470,15 @@
         <v>29400</v>
       </c>
       <c r="AG181" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="182" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A182" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B182" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C182" s="1">
         <v>60</v>
@@ -12497,7 +12497,7 @@
         <v>909005</v>
       </c>
       <c r="O182" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P182" s="1">
         <f t="shared" si="10"/>
@@ -12513,7 +12513,7 @@
         <v>608001</v>
       </c>
       <c r="X182" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y182" s="1">
         <v>600</v>
@@ -12522,7 +12522,7 @@
         <v>612003</v>
       </c>
       <c r="AA182" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB182" s="1">
         <v>4800</v>
@@ -12535,15 +12535,15 @@
         <v>30000</v>
       </c>
       <c r="AG182" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="183" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A183" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B183" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C183" s="1">
         <v>61</v>
@@ -12562,7 +12562,7 @@
         <v>909005</v>
       </c>
       <c r="O183" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P183" s="1">
         <f t="shared" si="10"/>
@@ -12578,7 +12578,7 @@
         <v>608001</v>
       </c>
       <c r="X183" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y183" s="1">
         <v>610</v>
@@ -12587,7 +12587,7 @@
         <v>612001</v>
       </c>
       <c r="AA183" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB183" s="1">
         <v>4900</v>
@@ -12600,15 +12600,15 @@
         <v>30600</v>
       </c>
       <c r="AG183" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="184" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A184" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B184" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C184" s="1">
         <v>62</v>
@@ -12627,7 +12627,7 @@
         <v>909005</v>
       </c>
       <c r="O184" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P184" s="1">
         <f t="shared" si="10"/>
@@ -12643,7 +12643,7 @@
         <v>608001</v>
       </c>
       <c r="X184" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y184" s="1">
         <v>620</v>
@@ -12652,7 +12652,7 @@
         <v>612002</v>
       </c>
       <c r="AA184" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB184" s="1">
         <v>5000</v>
@@ -12665,15 +12665,15 @@
         <v>31200</v>
       </c>
       <c r="AG184" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="185" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A185" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B185" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C185" s="1">
         <v>63</v>
@@ -12692,7 +12692,7 @@
         <v>909005</v>
       </c>
       <c r="O185" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P185" s="1">
         <f t="shared" si="10"/>
@@ -12708,7 +12708,7 @@
         <v>608001</v>
       </c>
       <c r="X185" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y185" s="1">
         <v>630</v>
@@ -12717,7 +12717,7 @@
         <v>612003</v>
       </c>
       <c r="AA185" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB185" s="1">
         <v>5100</v>
@@ -12730,15 +12730,15 @@
         <v>31800</v>
       </c>
       <c r="AG185" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="186" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A186" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B186" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C186" s="1">
         <v>64</v>
@@ -12757,7 +12757,7 @@
         <v>909005</v>
       </c>
       <c r="O186" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P186" s="1">
         <f t="shared" si="10"/>
@@ -12773,7 +12773,7 @@
         <v>608001</v>
       </c>
       <c r="X186" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y186" s="1">
         <v>640</v>
@@ -12782,7 +12782,7 @@
         <v>612001</v>
       </c>
       <c r="AA186" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB186" s="1">
         <v>5200</v>
@@ -12795,15 +12795,15 @@
         <v>32400</v>
       </c>
       <c r="AG186" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="187" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A187" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B187" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C187" s="1">
         <v>65</v>
@@ -12822,7 +12822,7 @@
         <v>909005</v>
       </c>
       <c r="O187" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P187" s="1">
         <f t="shared" si="10"/>
@@ -12838,7 +12838,7 @@
         <v>608001</v>
       </c>
       <c r="X187" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y187" s="1">
         <v>650</v>
@@ -12847,7 +12847,7 @@
         <v>612002</v>
       </c>
       <c r="AA187" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB187" s="1">
         <v>5300</v>
@@ -12860,15 +12860,15 @@
         <v>33000</v>
       </c>
       <c r="AG187" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="188" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A188" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B188" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C188" s="1">
         <v>66</v>
@@ -12887,7 +12887,7 @@
         <v>909005</v>
       </c>
       <c r="O188" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P188" s="1">
         <f t="shared" si="10"/>
@@ -12903,7 +12903,7 @@
         <v>608001</v>
       </c>
       <c r="X188" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y188" s="1">
         <v>660</v>
@@ -12912,7 +12912,7 @@
         <v>612003</v>
       </c>
       <c r="AA188" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB188" s="1">
         <v>5400</v>
@@ -12925,15 +12925,15 @@
         <v>33600</v>
       </c>
       <c r="AG188" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="189" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A189" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B189" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C189" s="1">
         <v>67</v>
@@ -12952,7 +12952,7 @@
         <v>909005</v>
       </c>
       <c r="O189" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P189" s="1">
         <f t="shared" si="10"/>
@@ -12968,7 +12968,7 @@
         <v>608001</v>
       </c>
       <c r="X189" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y189" s="1">
         <v>670</v>
@@ -12977,7 +12977,7 @@
         <v>612001</v>
       </c>
       <c r="AA189" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB189" s="1">
         <v>5500</v>
@@ -12990,15 +12990,15 @@
         <v>34200</v>
       </c>
       <c r="AG189" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="190" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A190" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B190" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C190" s="1">
         <v>68</v>
@@ -13017,7 +13017,7 @@
         <v>909005</v>
       </c>
       <c r="O190" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P190" s="1">
         <f t="shared" si="10"/>
@@ -13033,7 +13033,7 @@
         <v>608001</v>
       </c>
       <c r="X190" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y190" s="1">
         <v>680</v>
@@ -13042,7 +13042,7 @@
         <v>612002</v>
       </c>
       <c r="AA190" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB190" s="1">
         <v>5600</v>
@@ -13055,15 +13055,15 @@
         <v>34800</v>
       </c>
       <c r="AG190" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="191" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A191" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B191" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C191" s="1">
         <v>69</v>
@@ -13082,7 +13082,7 @@
         <v>909005</v>
       </c>
       <c r="O191" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P191" s="1">
         <f t="shared" ref="P191:P222" si="12">P188+1</f>
@@ -13098,7 +13098,7 @@
         <v>608001</v>
       </c>
       <c r="X191" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y191" s="1">
         <v>690</v>
@@ -13107,7 +13107,7 @@
         <v>612003</v>
       </c>
       <c r="AA191" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB191" s="1">
         <v>5700</v>
@@ -13120,15 +13120,15 @@
         <v>35400</v>
       </c>
       <c r="AG191" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="192" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A192" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B192" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C192" s="1">
         <v>70</v>
@@ -13147,7 +13147,7 @@
         <v>909005</v>
       </c>
       <c r="O192" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P192" s="1">
         <f t="shared" si="12"/>
@@ -13163,7 +13163,7 @@
         <v>608001</v>
       </c>
       <c r="X192" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y192" s="1">
         <v>700</v>
@@ -13172,7 +13172,7 @@
         <v>612001</v>
       </c>
       <c r="AA192" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB192" s="1">
         <v>5800</v>
@@ -13185,15 +13185,15 @@
         <v>36000</v>
       </c>
       <c r="AG192" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="193" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A193" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B193" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C193" s="1">
         <v>71</v>
@@ -13212,7 +13212,7 @@
         <v>909005</v>
       </c>
       <c r="O193" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P193" s="1">
         <f t="shared" si="12"/>
@@ -13228,7 +13228,7 @@
         <v>608001</v>
       </c>
       <c r="X193" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y193" s="1">
         <v>710</v>
@@ -13237,7 +13237,7 @@
         <v>612002</v>
       </c>
       <c r="AA193" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB193" s="1">
         <v>5900</v>
@@ -13250,15 +13250,15 @@
         <v>36600</v>
       </c>
       <c r="AG193" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="194" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A194" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B194" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="C194" s="9">
         <v>72</v>
@@ -13277,7 +13277,7 @@
         <v>909005</v>
       </c>
       <c r="O194" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P194" s="9">
         <f t="shared" si="12"/>
@@ -13293,7 +13293,7 @@
         <v>608001</v>
       </c>
       <c r="X194" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y194" s="9">
         <v>720</v>
@@ -13302,7 +13302,7 @@
         <v>612003</v>
       </c>
       <c r="AA194" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB194" s="9">
         <v>6000</v>
@@ -13315,15 +13315,15 @@
         <v>37200</v>
       </c>
       <c r="AG194" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="195" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A195" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B195" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C195" s="1">
         <v>73</v>
@@ -13342,7 +13342,7 @@
         <v>909005</v>
       </c>
       <c r="O195" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P195" s="1">
         <f t="shared" si="12"/>
@@ -13358,7 +13358,7 @@
         <v>608001</v>
       </c>
       <c r="X195" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y195" s="1">
         <v>730</v>
@@ -13367,7 +13367,7 @@
         <v>612001</v>
       </c>
       <c r="AA195" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB195" s="1">
         <v>6100</v>
@@ -13380,15 +13380,15 @@
         <v>37800</v>
       </c>
       <c r="AG195" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="196" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A196" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B196" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C196" s="1">
         <v>74</v>
@@ -13407,7 +13407,7 @@
         <v>909005</v>
       </c>
       <c r="O196" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P196" s="1">
         <f t="shared" si="12"/>
@@ -13423,7 +13423,7 @@
         <v>608001</v>
       </c>
       <c r="X196" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y196" s="1">
         <v>740</v>
@@ -13432,7 +13432,7 @@
         <v>612002</v>
       </c>
       <c r="AA196" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB196" s="1">
         <v>6200</v>
@@ -13445,15 +13445,15 @@
         <v>38400</v>
       </c>
       <c r="AG196" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="197" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A197" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B197" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C197" s="1">
         <v>75</v>
@@ -13472,7 +13472,7 @@
         <v>909005</v>
       </c>
       <c r="O197" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P197" s="1">
         <f t="shared" si="12"/>
@@ -13488,7 +13488,7 @@
         <v>608001</v>
       </c>
       <c r="X197" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y197" s="1">
         <v>750</v>
@@ -13497,7 +13497,7 @@
         <v>612003</v>
       </c>
       <c r="AA197" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB197" s="1">
         <v>6300</v>
@@ -13510,15 +13510,15 @@
         <v>39000</v>
       </c>
       <c r="AG197" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="198" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A198" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B198" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B198" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C198" s="1">
         <v>76</v>
@@ -13537,7 +13537,7 @@
         <v>909005</v>
       </c>
       <c r="O198" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P198" s="1">
         <f t="shared" si="12"/>
@@ -13553,7 +13553,7 @@
         <v>608001</v>
       </c>
       <c r="X198" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y198" s="1">
         <v>760</v>
@@ -13562,7 +13562,7 @@
         <v>612001</v>
       </c>
       <c r="AA198" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB198" s="1">
         <v>6400</v>
@@ -13575,15 +13575,15 @@
         <v>39600</v>
       </c>
       <c r="AG198" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="199" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A199" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B199" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C199" s="1">
         <v>77</v>
@@ -13602,7 +13602,7 @@
         <v>909005</v>
       </c>
       <c r="O199" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P199" s="1">
         <f t="shared" si="12"/>
@@ -13618,7 +13618,7 @@
         <v>608001</v>
       </c>
       <c r="X199" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y199" s="1">
         <v>770</v>
@@ -13627,7 +13627,7 @@
         <v>612002</v>
       </c>
       <c r="AA199" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB199" s="1">
         <v>6500</v>
@@ -13640,15 +13640,15 @@
         <v>40200</v>
       </c>
       <c r="AG199" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="200" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A200" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B200" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C200" s="1">
         <v>78</v>
@@ -13667,7 +13667,7 @@
         <v>909005</v>
       </c>
       <c r="O200" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P200" s="1">
         <f t="shared" si="12"/>
@@ -13683,7 +13683,7 @@
         <v>608001</v>
       </c>
       <c r="X200" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y200" s="1">
         <v>780</v>
@@ -13692,7 +13692,7 @@
         <v>612003</v>
       </c>
       <c r="AA200" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB200" s="1">
         <v>6600</v>
@@ -13705,15 +13705,15 @@
         <v>40800</v>
       </c>
       <c r="AG200" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="201" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A201" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B201" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C201" s="1">
         <v>79</v>
@@ -13732,7 +13732,7 @@
         <v>909005</v>
       </c>
       <c r="O201" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P201" s="1">
         <f t="shared" si="12"/>
@@ -13748,7 +13748,7 @@
         <v>608001</v>
       </c>
       <c r="X201" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y201" s="1">
         <v>790</v>
@@ -13757,7 +13757,7 @@
         <v>612001</v>
       </c>
       <c r="AA201" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB201" s="1">
         <v>6700</v>
@@ -13770,15 +13770,15 @@
         <v>41400</v>
       </c>
       <c r="AG201" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="202" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A202" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B202" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C202" s="1">
         <v>80</v>
@@ -13797,7 +13797,7 @@
         <v>909005</v>
       </c>
       <c r="O202" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P202" s="1">
         <f t="shared" si="12"/>
@@ -13813,7 +13813,7 @@
         <v>608001</v>
       </c>
       <c r="X202" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y202" s="1">
         <v>800</v>
@@ -13822,7 +13822,7 @@
         <v>612002</v>
       </c>
       <c r="AA202" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB202" s="1">
         <v>6800</v>
@@ -13835,15 +13835,15 @@
         <v>42000</v>
       </c>
       <c r="AG202" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="203" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A203" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B203" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C203" s="1">
         <v>81</v>
@@ -13862,7 +13862,7 @@
         <v>909005</v>
       </c>
       <c r="O203" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P203" s="1">
         <f t="shared" si="12"/>
@@ -13878,7 +13878,7 @@
         <v>608001</v>
       </c>
       <c r="X203" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y203" s="1">
         <v>810</v>
@@ -13887,7 +13887,7 @@
         <v>612003</v>
       </c>
       <c r="AA203" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB203" s="1">
         <v>6900</v>
@@ -13900,15 +13900,15 @@
         <v>42600</v>
       </c>
       <c r="AG203" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="204" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A204" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B204" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C204" s="1">
         <v>82</v>
@@ -13927,7 +13927,7 @@
         <v>909005</v>
       </c>
       <c r="O204" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P204" s="1">
         <f t="shared" si="12"/>
@@ -13943,7 +13943,7 @@
         <v>608001</v>
       </c>
       <c r="X204" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y204" s="1">
         <v>820</v>
@@ -13952,7 +13952,7 @@
         <v>612001</v>
       </c>
       <c r="AA204" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB204" s="1">
         <v>7000</v>
@@ -13965,15 +13965,15 @@
         <v>43200</v>
       </c>
       <c r="AG204" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="205" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A205" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B205" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C205" s="1">
         <v>83</v>
@@ -13992,7 +13992,7 @@
         <v>909005</v>
       </c>
       <c r="O205" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P205" s="1">
         <f t="shared" si="12"/>
@@ -14008,7 +14008,7 @@
         <v>608001</v>
       </c>
       <c r="X205" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y205" s="1">
         <v>830</v>
@@ -14017,7 +14017,7 @@
         <v>612002</v>
       </c>
       <c r="AA205" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB205" s="1">
         <v>7100</v>
@@ -14030,15 +14030,15 @@
         <v>43800</v>
       </c>
       <c r="AG205" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="206" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A206" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B206" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C206" s="1">
         <v>84</v>
@@ -14057,7 +14057,7 @@
         <v>909005</v>
       </c>
       <c r="O206" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P206" s="1">
         <f t="shared" si="12"/>
@@ -14073,7 +14073,7 @@
         <v>608001</v>
       </c>
       <c r="X206" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y206" s="1">
         <v>840</v>
@@ -14082,7 +14082,7 @@
         <v>612003</v>
       </c>
       <c r="AA206" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB206" s="1">
         <v>7200</v>
@@ -14095,15 +14095,15 @@
         <v>44400</v>
       </c>
       <c r="AG206" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="207" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A207" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B207" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C207" s="1">
         <v>85</v>
@@ -14122,7 +14122,7 @@
         <v>909005</v>
       </c>
       <c r="O207" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P207" s="1">
         <f t="shared" si="12"/>
@@ -14138,7 +14138,7 @@
         <v>608001</v>
       </c>
       <c r="X207" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y207" s="1">
         <v>850</v>
@@ -14147,7 +14147,7 @@
         <v>612001</v>
       </c>
       <c r="AA207" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB207" s="1">
         <v>7300</v>
@@ -14160,15 +14160,15 @@
         <v>45000</v>
       </c>
       <c r="AG207" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="208" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A208" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B208" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C208" s="1">
         <v>86</v>
@@ -14187,7 +14187,7 @@
         <v>909005</v>
       </c>
       <c r="O208" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P208" s="1">
         <f t="shared" si="12"/>
@@ -14203,7 +14203,7 @@
         <v>608001</v>
       </c>
       <c r="X208" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y208" s="1">
         <v>860</v>
@@ -14212,7 +14212,7 @@
         <v>612002</v>
       </c>
       <c r="AA208" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB208" s="1">
         <v>7400</v>
@@ -14225,15 +14225,15 @@
         <v>45600</v>
       </c>
       <c r="AG208" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A209" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B209" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C209" s="1">
         <v>87</v>
@@ -14252,7 +14252,7 @@
         <v>909005</v>
       </c>
       <c r="O209" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P209" s="1">
         <f t="shared" si="12"/>
@@ -14268,7 +14268,7 @@
         <v>608001</v>
       </c>
       <c r="X209" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y209" s="1">
         <v>870</v>
@@ -14277,7 +14277,7 @@
         <v>612003</v>
       </c>
       <c r="AA209" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB209" s="1">
         <v>7500</v>
@@ -14290,15 +14290,15 @@
         <v>46200</v>
       </c>
       <c r="AG209" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="210" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A210" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B210" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C210" s="1">
         <v>88</v>
@@ -14317,7 +14317,7 @@
         <v>909005</v>
       </c>
       <c r="O210" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P210" s="1">
         <f t="shared" si="12"/>
@@ -14333,7 +14333,7 @@
         <v>608001</v>
       </c>
       <c r="X210" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y210" s="1">
         <v>880</v>
@@ -14342,7 +14342,7 @@
         <v>612001</v>
       </c>
       <c r="AA210" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB210" s="1">
         <v>7600</v>
@@ -14355,15 +14355,15 @@
         <v>46800</v>
       </c>
       <c r="AG210" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="211" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A211" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B211" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C211" s="1">
         <v>89</v>
@@ -14382,7 +14382,7 @@
         <v>909005</v>
       </c>
       <c r="O211" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P211" s="1">
         <f t="shared" si="12"/>
@@ -14398,7 +14398,7 @@
         <v>608001</v>
       </c>
       <c r="X211" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y211" s="1">
         <v>890</v>
@@ -14407,7 +14407,7 @@
         <v>612002</v>
       </c>
       <c r="AA211" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB211" s="1">
         <v>7700</v>
@@ -14420,15 +14420,15 @@
         <v>47400</v>
       </c>
       <c r="AG211" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="212" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A212" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B212" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C212" s="1">
         <v>90</v>
@@ -14447,7 +14447,7 @@
         <v>909005</v>
       </c>
       <c r="O212" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P212" s="1">
         <f t="shared" si="12"/>
@@ -14463,7 +14463,7 @@
         <v>608001</v>
       </c>
       <c r="X212" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y212" s="1">
         <v>900</v>
@@ -14472,7 +14472,7 @@
         <v>612003</v>
       </c>
       <c r="AA212" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB212" s="1">
         <v>7800</v>
@@ -14485,15 +14485,15 @@
         <v>48000</v>
       </c>
       <c r="AG212" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="213" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A213" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B213" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C213" s="1">
         <v>91</v>
@@ -14512,7 +14512,7 @@
         <v>909005</v>
       </c>
       <c r="O213" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P213" s="1">
         <f t="shared" si="12"/>
@@ -14528,7 +14528,7 @@
         <v>608001</v>
       </c>
       <c r="X213" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y213" s="1">
         <v>910</v>
@@ -14537,7 +14537,7 @@
         <v>612001</v>
       </c>
       <c r="AA213" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB213" s="1">
         <v>7900</v>
@@ -14550,15 +14550,15 @@
         <v>48600</v>
       </c>
       <c r="AG213" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="214" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A214" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B214" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C214" s="1">
         <v>92</v>
@@ -14577,7 +14577,7 @@
         <v>909005</v>
       </c>
       <c r="O214" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P214" s="1">
         <f t="shared" si="12"/>
@@ -14593,7 +14593,7 @@
         <v>608001</v>
       </c>
       <c r="X214" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y214" s="1">
         <v>920</v>
@@ -14602,7 +14602,7 @@
         <v>612002</v>
       </c>
       <c r="AA214" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB214" s="1">
         <v>8000</v>
@@ -14615,15 +14615,15 @@
         <v>49200</v>
       </c>
       <c r="AG214" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="215" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A215" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B215" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C215" s="1">
         <v>93</v>
@@ -14642,7 +14642,7 @@
         <v>909005</v>
       </c>
       <c r="O215" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P215" s="1">
         <f t="shared" si="12"/>
@@ -14658,7 +14658,7 @@
         <v>608001</v>
       </c>
       <c r="X215" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y215" s="1">
         <v>930</v>
@@ -14667,7 +14667,7 @@
         <v>612003</v>
       </c>
       <c r="AA215" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB215" s="1">
         <v>8100</v>
@@ -14680,15 +14680,15 @@
         <v>49800</v>
       </c>
       <c r="AG215" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="216" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A216" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B216" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C216" s="1">
         <v>94</v>
@@ -14707,7 +14707,7 @@
         <v>909005</v>
       </c>
       <c r="O216" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P216" s="1">
         <f t="shared" si="12"/>
@@ -14723,7 +14723,7 @@
         <v>608001</v>
       </c>
       <c r="X216" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y216" s="1">
         <v>940</v>
@@ -14732,7 +14732,7 @@
         <v>612001</v>
       </c>
       <c r="AA216" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB216" s="1">
         <v>8200</v>
@@ -14745,15 +14745,15 @@
         <v>50400</v>
       </c>
       <c r="AG216" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="217" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A217" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B217" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C217" s="1">
         <v>95</v>
@@ -14772,7 +14772,7 @@
         <v>909005</v>
       </c>
       <c r="O217" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P217" s="1">
         <f t="shared" si="12"/>
@@ -14788,7 +14788,7 @@
         <v>608001</v>
       </c>
       <c r="X217" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y217" s="1">
         <v>950</v>
@@ -14797,7 +14797,7 @@
         <v>612002</v>
       </c>
       <c r="AA217" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB217" s="1">
         <v>8300</v>
@@ -14810,15 +14810,15 @@
         <v>51000</v>
       </c>
       <c r="AG217" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="218" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A218" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B218" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C218" s="1">
         <v>96</v>
@@ -14837,7 +14837,7 @@
         <v>909005</v>
       </c>
       <c r="O218" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P218" s="1">
         <f t="shared" si="12"/>
@@ -14853,7 +14853,7 @@
         <v>608001</v>
       </c>
       <c r="X218" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y218" s="1">
         <v>960</v>
@@ -14862,7 +14862,7 @@
         <v>612003</v>
       </c>
       <c r="AA218" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB218" s="1">
         <v>8400</v>
@@ -14875,15 +14875,15 @@
         <v>51600</v>
       </c>
       <c r="AG218" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="219" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A219" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B219" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C219" s="1">
         <v>97</v>
@@ -14902,7 +14902,7 @@
         <v>909005</v>
       </c>
       <c r="O219" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P219" s="1">
         <f t="shared" si="12"/>
@@ -14918,7 +14918,7 @@
         <v>608001</v>
       </c>
       <c r="X219" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y219" s="1">
         <v>970</v>
@@ -14927,7 +14927,7 @@
         <v>612001</v>
       </c>
       <c r="AA219" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB219" s="1">
         <v>8500</v>
@@ -14940,15 +14940,15 @@
         <v>52200</v>
       </c>
       <c r="AG219" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="220" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A220" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B220" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C220" s="1">
         <v>98</v>
@@ -14967,7 +14967,7 @@
         <v>909005</v>
       </c>
       <c r="O220" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P220" s="1">
         <f t="shared" si="12"/>
@@ -14983,7 +14983,7 @@
         <v>608001</v>
       </c>
       <c r="X220" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y220" s="1">
         <v>980</v>
@@ -14992,7 +14992,7 @@
         <v>612002</v>
       </c>
       <c r="AA220" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB220" s="1">
         <v>8600</v>
@@ -15005,15 +15005,15 @@
         <v>52800</v>
       </c>
       <c r="AG220" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="221" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A221" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B221" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C221" s="1">
         <v>99</v>
@@ -15032,7 +15032,7 @@
         <v>909005</v>
       </c>
       <c r="O221" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P221" s="1">
         <f t="shared" si="12"/>
@@ -15048,7 +15048,7 @@
         <v>608001</v>
       </c>
       <c r="X221" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y221" s="1">
         <v>990</v>
@@ -15057,7 +15057,7 @@
         <v>612003</v>
       </c>
       <c r="AA221" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB221" s="1">
         <v>9000</v>
@@ -15070,15 +15070,15 @@
         <v>54900</v>
       </c>
       <c r="AG221" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="222" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A222" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B222" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C222" s="1">
         <v>100</v>
@@ -15097,7 +15097,7 @@
         <v>909005</v>
       </c>
       <c r="O222" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P222" s="1">
         <f t="shared" si="12"/>
@@ -15113,7 +15113,7 @@
         <v>608001</v>
       </c>
       <c r="X222" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y222" s="1">
         <v>1000</v>
@@ -15122,7 +15122,7 @@
         <v>612001</v>
       </c>
       <c r="AA222" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AB222" s="1">
         <v>10000</v>
@@ -15135,7 +15135,7 @@
         <v>60000</v>
       </c>
       <c r="AG222" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
